--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5534" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5560" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -268,8 +268,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -499,6 +499,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Bundle.meta.tag</t>
   </si>
   <si>
@@ -580,6 +590,12 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -713,6 +729,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -720,6 +739,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -738,8 +760,8 @@
 </t>
   </si>
   <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -788,6 +810,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -797,8 +822,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -854,8 +879,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -909,6 +934,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -936,8 +964,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1723,8 +1751,8 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="57.64453125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -3083,16 +3111,16 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3103,10 +3131,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3132,13 +3160,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3164,13 +3192,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3188,7 +3216,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3197,16 +3225,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3217,10 +3245,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3246,13 +3274,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3302,7 +3330,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3331,10 +3359,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3357,16 +3385,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3392,13 +3420,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3416,7 +3444,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3445,10 +3473,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3471,16 +3499,16 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3530,7 +3558,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3539,30 +3567,30 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3585,16 +3613,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3602,7 +3630,7 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>77</v>
@@ -3620,31 +3648,31 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>87</v>
@@ -3668,15 +3696,15 @@
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3702,13 +3730,13 @@
         <v>123</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3758,7 +3786,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3779,18 +3807,18 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3813,16 +3841,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3872,7 +3900,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3881,7 +3909,7 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
@@ -3901,10 +3929,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3927,16 +3955,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3986,7 +4014,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3995,7 +4023,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
@@ -4004,7 +4032,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4015,10 +4043,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4127,10 +4155,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4200,16 +4228,16 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>115</v>
@@ -4241,14 +4269,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4270,16 +4298,16 @@
         <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4328,7 +4356,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4357,10 +4385,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4386,12 +4414,14 @@
         <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4440,7 +4470,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4469,10 +4499,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4498,12 +4528,14 @@
         <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4552,7 +4584,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>87</v>
@@ -4581,10 +4613,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4592,7 +4624,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4607,13 +4639,13 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4652,7 +4684,7 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -4662,7 +4694,7 @@
         <v>141</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4671,16 +4703,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4691,10 +4723,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4803,10 +4835,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4876,16 +4908,16 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>115</v>
@@ -4917,14 +4949,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4946,16 +4978,16 @@
         <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5004,7 +5036,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5033,10 +5065,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5062,10 +5094,10 @@
         <v>77</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5116,7 +5148,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5128,7 +5160,7 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5145,10 +5177,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5174,13 +5206,13 @@
         <v>129</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5230,7 +5262,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5259,10 +5291,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5285,13 +5317,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5342,7 +5374,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5360,7 +5392,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5371,10 +5403,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5397,13 +5429,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5454,7 +5486,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5463,7 +5495,7 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
@@ -5472,7 +5504,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5483,10 +5515,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5595,10 +5627,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5668,16 +5700,16 @@
         <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>115</v>
@@ -5709,14 +5741,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5738,16 +5770,16 @@
         <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5796,7 +5828,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5825,10 +5857,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5851,16 +5883,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5886,13 +5918,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5910,7 +5942,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5939,10 +5971,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5965,16 +5997,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6024,7 +6056,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6033,7 +6065,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -6042,7 +6074,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6053,10 +6085,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6079,13 +6111,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6136,7 +6168,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6145,7 +6177,7 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
@@ -6154,7 +6186,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6165,10 +6197,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6277,10 +6309,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6350,16 +6382,16 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>115</v>
@@ -6391,14 +6423,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6420,16 +6452,16 @@
         <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6478,7 +6510,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6507,10 +6539,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6533,13 +6565,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6566,13 +6598,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6590,7 +6622,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6619,10 +6651,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6648,13 +6680,13 @@
         <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6704,7 +6736,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6733,10 +6765,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6762,12 +6794,14 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6816,7 +6850,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6845,10 +6879,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6874,12 +6908,14 @@
         <v>123</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6928,7 +6964,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6957,10 +6993,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6986,12 +7022,14 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7040,7 +7078,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7069,10 +7107,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7098,12 +7136,14 @@
         <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7152,7 +7192,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7181,10 +7221,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7207,13 +7247,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7264,7 +7304,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7273,7 +7313,7 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
@@ -7282,7 +7322,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7293,10 +7333,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7405,10 +7445,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7478,16 +7518,16 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>115</v>
@@ -7519,14 +7559,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7548,16 +7588,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7606,7 +7646,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7635,10 +7675,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7664,12 +7704,14 @@
         <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7718,7 +7760,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -7747,10 +7789,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7776,12 +7818,14 @@
         <v>129</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7830,7 +7874,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7859,10 +7903,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7888,13 +7932,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7944,7 +7988,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7973,10 +8017,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8002,13 +8046,13 @@
         <v>123</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8058,7 +8102,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8087,10 +8131,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8113,16 +8157,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8172,7 +8216,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8190,7 +8234,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8201,13 +8245,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>77</v>
@@ -8229,13 +8273,13 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8286,7 +8330,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8295,16 +8339,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8315,10 +8359,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8427,10 +8471,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8500,16 +8544,16 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>115</v>
@@ -8541,14 +8585,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8570,16 +8614,16 @@
         <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8628,7 +8672,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8657,10 +8701,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8686,10 +8730,10 @@
         <v>77</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8740,7 +8784,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8752,7 +8796,7 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8769,10 +8813,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8798,13 +8842,13 @@
         <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8854,7 +8898,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8883,10 +8927,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8909,16 +8953,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8968,7 +9012,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8986,10 +9030,10 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8997,10 +9041,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9023,13 +9067,13 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9080,7 +9124,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9089,7 +9133,7 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
@@ -9098,7 +9142,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9109,10 +9153,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9221,10 +9265,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9294,16 +9338,16 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>115</v>
@@ -9335,14 +9379,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9364,16 +9408,16 @@
         <v>108</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9422,7 +9466,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9451,10 +9495,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9477,16 +9521,16 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9512,13 +9556,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9536,7 +9580,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9565,10 +9609,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9591,16 +9635,16 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9650,7 +9694,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9659,7 +9703,7 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
@@ -9668,7 +9712,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9679,10 +9723,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9705,13 +9749,13 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9762,7 +9806,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9771,7 +9815,7 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>99</v>
@@ -9780,7 +9824,7 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9791,10 +9835,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9903,10 +9947,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9976,16 +10020,16 @@
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>115</v>
@@ -10017,14 +10061,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10046,16 +10090,16 @@
         <v>108</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10104,7 +10148,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10133,10 +10177,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10159,13 +10203,13 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10192,13 +10236,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10216,7 +10260,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>87</v>
@@ -10245,10 +10289,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10274,13 +10318,13 @@
         <v>129</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10330,7 +10374,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10359,10 +10403,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10388,12 +10432,14 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10442,7 +10488,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10471,10 +10517,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10500,12 +10546,14 @@
         <v>123</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10554,7 +10602,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10583,10 +10631,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10612,12 +10660,14 @@
         <v>101</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -10666,7 +10716,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10695,10 +10745,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10724,12 +10774,14 @@
         <v>101</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -10778,7 +10830,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10807,10 +10859,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10833,13 +10885,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10890,7 +10942,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10899,7 +10951,7 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>99</v>
@@ -10908,7 +10960,7 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10919,10 +10971,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11031,10 +11083,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11104,16 +11156,16 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>115</v>
@@ -11145,14 +11197,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11174,16 +11226,16 @@
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11232,7 +11284,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11261,10 +11313,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11290,12 +11342,14 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -11344,7 +11398,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -11373,10 +11427,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11402,12 +11456,14 @@
         <v>129</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -11456,7 +11512,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11485,10 +11541,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11514,13 +11570,13 @@
         <v>101</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11570,7 +11626,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11599,10 +11655,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11628,13 +11684,13 @@
         <v>123</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11684,7 +11740,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11713,10 +11769,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11739,16 +11795,16 @@
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11798,7 +11854,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11816,7 +11872,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11827,13 +11883,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>77</v>
@@ -11855,13 +11911,13 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11912,7 +11968,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11921,16 +11977,16 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11941,10 +11997,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12053,10 +12109,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12126,16 +12182,16 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>115</v>
@@ -12167,14 +12223,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12196,16 +12252,16 @@
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12254,7 +12310,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12283,10 +12339,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12312,10 +12368,10 @@
         <v>77</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12366,7 +12422,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12378,7 +12434,7 @@
         <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
@@ -12395,10 +12451,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12424,13 +12480,13 @@
         <v>129</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12480,7 +12536,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12509,10 +12565,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12535,13 +12591,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12592,7 +12648,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12610,7 +12666,7 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12621,10 +12677,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12647,13 +12703,13 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12704,7 +12760,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12713,7 +12769,7 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>99</v>
@@ -12722,7 +12778,7 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -12733,10 +12789,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12845,10 +12901,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12918,16 +12974,16 @@
         <v>77</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>115</v>
@@ -12959,14 +13015,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12988,16 +13044,16 @@
         <v>108</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13046,7 +13102,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13075,10 +13131,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13101,16 +13157,16 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13136,13 +13192,13 @@
         <v>77</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>77</v>
@@ -13160,7 +13216,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13189,10 +13245,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13215,16 +13271,16 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13274,7 +13330,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13283,7 +13339,7 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>99</v>
@@ -13292,7 +13348,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13303,10 +13359,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13329,13 +13385,13 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13386,7 +13442,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13395,7 +13451,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -13404,7 +13460,7 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13415,10 +13471,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13527,10 +13583,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13600,16 +13656,16 @@
         <v>77</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>115</v>
@@ -13641,14 +13697,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13670,16 +13726,16 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -13728,7 +13784,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13757,10 +13813,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13783,13 +13839,13 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13816,13 +13872,13 @@
         <v>77</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>77</v>
@@ -13840,7 +13896,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>87</v>
@@ -13869,10 +13925,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13898,13 +13954,13 @@
         <v>129</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13954,7 +14010,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13983,10 +14039,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14012,12 +14068,14 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -14066,7 +14124,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14095,10 +14153,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14124,12 +14182,14 @@
         <v>123</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14178,7 +14238,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14207,10 +14267,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14236,12 +14296,14 @@
         <v>101</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14290,7 +14352,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14319,10 +14381,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14348,12 +14410,14 @@
         <v>101</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -14402,7 +14466,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14431,10 +14495,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14457,13 +14521,13 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14514,7 +14578,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14523,7 +14587,7 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>99</v>
@@ -14532,7 +14596,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14543,10 +14607,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14655,10 +14719,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14728,16 +14792,16 @@
         <v>77</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>115</v>
@@ -14769,14 +14833,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14798,16 +14862,16 @@
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14856,7 +14920,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -14885,10 +14949,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14914,12 +14978,14 @@
         <v>101</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -14968,7 +15034,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -14997,10 +15063,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15026,12 +15092,14 @@
         <v>129</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15080,7 +15148,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15109,10 +15177,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15138,13 +15206,13 @@
         <v>101</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15194,7 +15262,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15223,10 +15291,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15252,13 +15320,13 @@
         <v>123</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15308,7 +15376,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15337,10 +15405,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15363,16 +15431,16 @@
         <v>88</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -15422,7 +15490,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15440,7 +15508,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -15451,13 +15519,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>77</v>
@@ -15479,13 +15547,13 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15536,7 +15604,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15545,16 +15613,16 @@
         <v>79</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15565,10 +15633,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15677,10 +15745,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15750,16 +15818,16 @@
         <v>77</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>115</v>
@@ -15791,14 +15859,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -15820,16 +15888,16 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -15878,7 +15946,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -15907,10 +15975,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15936,10 +16004,10 @@
         <v>77</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15990,7 +16058,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16002,7 +16070,7 @@
         <v>77</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>77</v>
@@ -16019,10 +16087,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16048,13 +16116,13 @@
         <v>129</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16104,7 +16172,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16133,10 +16201,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16159,16 +16227,16 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16218,7 +16286,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16236,7 +16304,7 @@
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -16247,10 +16315,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16273,13 +16341,13 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -16330,7 +16398,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16339,7 +16407,7 @@
         <v>87</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>99</v>
@@ -16348,7 +16416,7 @@
         <v>77</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>77</v>
@@ -16359,10 +16427,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16471,10 +16539,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16544,16 +16612,16 @@
         <v>77</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF131" t="s" s="2">
         <v>115</v>
@@ -16585,14 +16653,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16614,16 +16682,16 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16672,7 +16740,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -16701,10 +16769,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16727,16 +16795,16 @@
         <v>88</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -16762,13 +16830,13 @@
         <v>77</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -16786,7 +16854,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -16815,10 +16883,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16841,16 +16909,16 @@
         <v>88</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16900,7 +16968,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -16909,7 +16977,7 @@
         <v>87</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -16918,7 +16986,7 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
@@ -16929,10 +16997,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16955,13 +17023,13 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17012,7 +17080,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17021,7 +17089,7 @@
         <v>87</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -17030,7 +17098,7 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
@@ -17041,10 +17109,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17153,10 +17221,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17226,16 +17294,16 @@
         <v>77</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF137" t="s" s="2">
         <v>115</v>
@@ -17267,14 +17335,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17296,16 +17364,16 @@
         <v>108</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -17354,7 +17422,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -17383,10 +17451,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17409,13 +17477,13 @@
         <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -17442,13 +17510,13 @@
         <v>77</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>77</v>
@@ -17466,7 +17534,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>87</v>
@@ -17495,10 +17563,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17524,13 +17592,13 @@
         <v>129</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -17580,7 +17648,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17609,10 +17677,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17638,12 +17706,14 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -17692,7 +17762,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -17721,10 +17791,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17750,12 +17820,14 @@
         <v>123</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -17804,7 +17876,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -17833,10 +17905,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17862,12 +17934,14 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -17916,7 +17990,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -17945,10 +18019,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17974,12 +18048,14 @@
         <v>101</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N144" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -18028,7 +18104,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18057,10 +18133,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18083,13 +18159,13 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18140,7 +18216,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18149,7 +18225,7 @@
         <v>87</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>99</v>
@@ -18158,7 +18234,7 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
@@ -18169,10 +18245,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18281,10 +18357,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18354,16 +18430,16 @@
         <v>77</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF147" t="s" s="2">
         <v>115</v>
@@ -18395,14 +18471,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -18424,16 +18500,16 @@
         <v>108</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -18482,7 +18558,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -18511,10 +18587,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18540,12 +18616,14 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -18594,7 +18672,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>87</v>
@@ -18623,10 +18701,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18652,12 +18730,14 @@
         <v>129</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N150" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -18706,7 +18786,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -18735,10 +18815,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18764,13 +18844,13 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -18820,7 +18900,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -18849,10 +18929,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18878,13 +18958,13 @@
         <v>123</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18934,7 +19014,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -18963,10 +19043,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18989,16 +19069,16 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19048,7 +19128,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -19066,7 +19146,7 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
@@ -19077,10 +19157,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19103,19 +19183,19 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -19164,7 +19244,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19173,7 +19253,7 @@
         <v>87</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>99</v>
@@ -19182,7 +19262,7 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5560" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5534" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -268,8 +268,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -499,16 +499,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Bundle.meta.tag</t>
   </si>
   <si>
@@ -590,12 +580,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -729,9 +713,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -739,9 +720,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -760,8 +738,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -810,9 +788,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -822,8 +797,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -879,8 +854,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -934,9 +909,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -964,8 +936,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1751,8 +1723,8 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="57.64453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -3111,16 +3083,16 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3131,10 +3103,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3160,13 +3132,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3192,31 +3164,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3225,16 +3197,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3245,10 +3217,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3274,13 +3246,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3330,7 +3302,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3359,10 +3331,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3385,16 +3357,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3420,31 +3392,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3473,10 +3445,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3499,16 +3471,16 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3558,7 +3530,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3567,30 +3539,30 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3613,16 +3585,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3630,7 +3602,7 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>77</v>
@@ -3648,13 +3620,13 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3672,7 +3644,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>87</v>
@@ -3696,15 +3668,15 @@
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3730,13 +3702,13 @@
         <v>123</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3786,7 +3758,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3807,18 +3779,18 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3841,16 +3813,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3900,16 +3872,16 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
@@ -3929,10 +3901,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3955,16 +3927,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4014,7 +3986,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4023,7 +3995,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
@@ -4032,7 +4004,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4043,10 +4015,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4155,10 +4127,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4228,16 +4200,16 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>115</v>
@@ -4269,14 +4241,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4298,16 +4270,16 @@
         <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4356,7 +4328,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4385,10 +4357,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4414,14 +4386,12 @@
         <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4470,7 +4440,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4499,10 +4469,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4528,14 +4498,12 @@
         <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4584,7 +4552,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>87</v>
@@ -4613,10 +4581,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4624,7 +4592,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4639,13 +4607,13 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4684,7 +4652,7 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -4694,7 +4662,7 @@
         <v>141</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4703,16 +4671,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4723,10 +4691,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4835,10 +4803,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4908,16 +4876,16 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>115</v>
@@ -4949,14 +4917,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4978,16 +4946,16 @@
         <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5036,7 +5004,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5065,10 +5033,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5094,10 +5062,10 @@
         <v>77</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5148,7 +5116,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5160,7 +5128,7 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5177,10 +5145,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5206,13 +5174,13 @@
         <v>129</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5262,7 +5230,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5291,10 +5259,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5317,13 +5285,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5374,7 +5342,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5392,7 +5360,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5403,10 +5371,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5429,13 +5397,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5486,7 +5454,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5495,7 +5463,7 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
@@ -5504,7 +5472,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5515,10 +5483,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5627,10 +5595,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5700,16 +5668,16 @@
         <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>115</v>
@@ -5741,14 +5709,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5770,16 +5738,16 @@
         <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5828,7 +5796,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5857,10 +5825,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5883,16 +5851,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5918,13 +5886,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5942,7 +5910,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5971,10 +5939,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5997,16 +5965,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6056,7 +6024,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6065,7 +6033,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -6074,7 +6042,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6085,10 +6053,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6111,13 +6079,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6168,7 +6136,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6177,7 +6145,7 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
@@ -6186,7 +6154,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6197,10 +6165,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6309,10 +6277,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6382,16 +6350,16 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>115</v>
@@ -6423,14 +6391,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6452,16 +6420,16 @@
         <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6510,7 +6478,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6539,10 +6507,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6565,13 +6533,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6598,13 +6566,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6622,7 +6590,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6651,10 +6619,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6680,13 +6648,13 @@
         <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6736,7 +6704,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6765,10 +6733,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6794,14 +6762,12 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6850,7 +6816,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6879,10 +6845,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6908,14 +6874,12 @@
         <v>123</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6964,7 +6928,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6993,10 +6957,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7022,14 +6986,12 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7078,7 +7040,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7107,10 +7069,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7136,14 +7098,12 @@
         <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7192,7 +7152,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7221,10 +7181,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7247,13 +7207,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7304,7 +7264,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7313,7 +7273,7 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
@@ -7322,7 +7282,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7333,10 +7293,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7445,10 +7405,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7518,16 +7478,16 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>115</v>
@@ -7559,14 +7519,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7588,16 +7548,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7646,7 +7606,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7675,10 +7635,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7704,14 +7664,12 @@
         <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7760,7 +7718,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -7789,10 +7747,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7818,14 +7776,12 @@
         <v>129</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7874,7 +7830,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7903,10 +7859,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7932,13 +7888,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7988,7 +7944,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8017,10 +7973,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8046,13 +8002,13 @@
         <v>123</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8102,7 +8058,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8131,10 +8087,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8157,16 +8113,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8216,7 +8172,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8234,7 +8190,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8245,13 +8201,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>77</v>
@@ -8273,13 +8229,13 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8330,7 +8286,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8339,16 +8295,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8359,10 +8315,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8471,10 +8427,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8544,16 +8500,16 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>115</v>
@@ -8585,14 +8541,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8614,16 +8570,16 @@
         <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8672,7 +8628,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8701,10 +8657,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8730,10 +8686,10 @@
         <v>77</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8784,7 +8740,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8796,7 +8752,7 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8813,10 +8769,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8842,13 +8798,13 @@
         <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8898,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8927,10 +8883,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8953,16 +8909,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9012,7 +8968,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9030,10 +8986,10 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9041,10 +8997,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9067,13 +9023,13 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9124,7 +9080,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9133,7 +9089,7 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
@@ -9142,7 +9098,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9153,10 +9109,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9265,10 +9221,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9338,16 +9294,16 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>115</v>
@@ -9379,14 +9335,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9408,16 +9364,16 @@
         <v>108</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9466,7 +9422,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9495,10 +9451,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9521,16 +9477,16 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9556,13 +9512,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9580,7 +9536,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9609,10 +9565,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9635,16 +9591,16 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9694,7 +9650,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9703,7 +9659,7 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
@@ -9712,7 +9668,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9723,10 +9679,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9749,13 +9705,13 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9806,7 +9762,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9815,7 +9771,7 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>99</v>
@@ -9824,7 +9780,7 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9835,10 +9791,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9947,10 +9903,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10020,16 +9976,16 @@
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>115</v>
@@ -10061,14 +10017,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10090,16 +10046,16 @@
         <v>108</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10148,7 +10104,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10177,10 +10133,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10203,13 +10159,13 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10236,13 +10192,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10260,7 +10216,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>87</v>
@@ -10289,10 +10245,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10318,13 +10274,13 @@
         <v>129</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10374,7 +10330,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10403,10 +10359,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10432,14 +10388,12 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10488,7 +10442,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10517,10 +10471,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10546,14 +10500,12 @@
         <v>123</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10602,7 +10554,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10631,10 +10583,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10660,14 +10612,12 @@
         <v>101</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -10716,7 +10666,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10745,10 +10695,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10774,14 +10724,12 @@
         <v>101</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -10830,7 +10778,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10859,10 +10807,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10885,13 +10833,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10942,7 +10890,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10951,7 +10899,7 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>99</v>
@@ -10960,7 +10908,7 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10971,10 +10919,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11083,10 +11031,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11156,16 +11104,16 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>115</v>
@@ -11197,14 +11145,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11226,16 +11174,16 @@
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11284,7 +11232,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11313,10 +11261,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11342,14 +11290,12 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -11398,7 +11344,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -11427,10 +11373,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11456,14 +11402,12 @@
         <v>129</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -11512,7 +11456,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11541,10 +11485,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11570,13 +11514,13 @@
         <v>101</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11626,7 +11570,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11655,10 +11599,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11684,13 +11628,13 @@
         <v>123</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11740,7 +11684,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11769,10 +11713,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11795,16 +11739,16 @@
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11854,7 +11798,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11872,7 +11816,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11883,13 +11827,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>77</v>
@@ -11911,13 +11855,13 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11968,7 +11912,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11977,16 +11921,16 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11997,10 +11941,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12109,10 +12053,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12182,16 +12126,16 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>115</v>
@@ -12223,14 +12167,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12252,16 +12196,16 @@
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12310,7 +12254,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12339,10 +12283,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12368,10 +12312,10 @@
         <v>77</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12422,7 +12366,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12434,7 +12378,7 @@
         <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
@@ -12451,10 +12395,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12480,13 +12424,13 @@
         <v>129</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12536,7 +12480,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12565,10 +12509,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12591,13 +12535,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12648,7 +12592,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12666,7 +12610,7 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12677,10 +12621,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12703,13 +12647,13 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12760,7 +12704,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12769,7 +12713,7 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>99</v>
@@ -12778,7 +12722,7 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -12789,10 +12733,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12901,10 +12845,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12974,16 +12918,16 @@
         <v>77</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>115</v>
@@ -13015,14 +12959,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13044,16 +12988,16 @@
         <v>108</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13102,7 +13046,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13131,10 +13075,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13157,16 +13101,16 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13192,13 +13136,13 @@
         <v>77</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>77</v>
@@ -13216,7 +13160,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13245,10 +13189,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13271,16 +13215,16 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13330,7 +13274,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13339,7 +13283,7 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>99</v>
@@ -13348,7 +13292,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13359,10 +13303,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13385,13 +13329,13 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13442,7 +13386,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13451,7 +13395,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -13460,7 +13404,7 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13471,10 +13415,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13583,10 +13527,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13656,16 +13600,16 @@
         <v>77</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>115</v>
@@ -13697,14 +13641,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13726,16 +13670,16 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -13784,7 +13728,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13813,10 +13757,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13839,13 +13783,13 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13872,13 +13816,13 @@
         <v>77</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>77</v>
@@ -13896,7 +13840,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>87</v>
@@ -13925,10 +13869,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13954,13 +13898,13 @@
         <v>129</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14010,7 +13954,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -14039,10 +13983,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14068,14 +14012,12 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -14124,7 +14066,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14153,10 +14095,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14182,14 +14124,12 @@
         <v>123</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14238,7 +14178,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14267,10 +14207,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14296,14 +14236,12 @@
         <v>101</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14352,7 +14290,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14381,10 +14319,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14410,14 +14348,12 @@
         <v>101</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -14466,7 +14402,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14495,10 +14431,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14521,13 +14457,13 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14578,7 +14514,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14587,7 +14523,7 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>99</v>
@@ -14596,7 +14532,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14607,10 +14543,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14719,10 +14655,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14792,16 +14728,16 @@
         <v>77</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>115</v>
@@ -14833,14 +14769,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14862,16 +14798,16 @@
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14920,7 +14856,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -14949,10 +14885,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14978,14 +14914,12 @@
         <v>101</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15034,7 +14968,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15063,10 +14997,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15092,14 +15026,12 @@
         <v>129</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15148,7 +15080,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15177,10 +15109,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15206,13 +15138,13 @@
         <v>101</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15262,7 +15194,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15291,10 +15223,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15320,13 +15252,13 @@
         <v>123</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15376,7 +15308,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15405,10 +15337,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15431,16 +15363,16 @@
         <v>88</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -15490,7 +15422,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15508,7 +15440,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -15519,13 +15451,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>77</v>
@@ -15547,13 +15479,13 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15604,7 +15536,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15613,16 +15545,16 @@
         <v>79</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15633,10 +15565,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15745,10 +15677,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15818,16 +15750,16 @@
         <v>77</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>115</v>
@@ -15859,14 +15791,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -15888,16 +15820,16 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -15946,7 +15878,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -15975,10 +15907,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16004,10 +15936,10 @@
         <v>77</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16058,7 +15990,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16070,7 +16002,7 @@
         <v>77</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>77</v>
@@ -16087,10 +16019,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16116,13 +16048,13 @@
         <v>129</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16172,7 +16104,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16201,10 +16133,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16227,16 +16159,16 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16286,7 +16218,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16304,7 +16236,7 @@
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -16315,10 +16247,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16341,13 +16273,13 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -16398,7 +16330,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16407,7 +16339,7 @@
         <v>87</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>99</v>
@@ -16416,7 +16348,7 @@
         <v>77</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>77</v>
@@ -16427,10 +16359,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16539,10 +16471,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16612,16 +16544,16 @@
         <v>77</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
         <v>115</v>
@@ -16653,14 +16585,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16682,16 +16614,16 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16740,7 +16672,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -16769,10 +16701,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16795,16 +16727,16 @@
         <v>88</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -16830,13 +16762,13 @@
         <v>77</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -16854,7 +16786,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -16883,10 +16815,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16909,16 +16841,16 @@
         <v>88</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16968,7 +16900,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -16977,7 +16909,7 @@
         <v>87</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -16986,7 +16918,7 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
@@ -16997,10 +16929,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17023,13 +16955,13 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17080,7 +17012,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17089,7 +17021,7 @@
         <v>87</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -17098,7 +17030,7 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
@@ -17109,10 +17041,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17221,10 +17153,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17294,16 +17226,16 @@
         <v>77</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
         <v>115</v>
@@ -17335,14 +17267,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17364,16 +17296,16 @@
         <v>108</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -17422,7 +17354,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -17451,10 +17383,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17477,13 +17409,13 @@
         <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -17510,13 +17442,13 @@
         <v>77</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>77</v>
@@ -17534,7 +17466,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>87</v>
@@ -17563,10 +17495,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17592,13 +17524,13 @@
         <v>129</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -17648,7 +17580,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17677,10 +17609,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17706,14 +17638,12 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -17762,7 +17692,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -17791,10 +17721,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17820,14 +17750,12 @@
         <v>123</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -17876,7 +17804,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -17905,10 +17833,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17934,14 +17862,12 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -17990,7 +17916,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18019,10 +17945,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18048,14 +17974,12 @@
         <v>101</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -18104,7 +18028,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18133,10 +18057,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18159,13 +18083,13 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18216,7 +18140,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18225,7 +18149,7 @@
         <v>87</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>99</v>
@@ -18234,7 +18158,7 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
@@ -18245,10 +18169,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18357,10 +18281,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18430,16 +18354,16 @@
         <v>77</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
         <v>115</v>
@@ -18471,14 +18395,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -18500,16 +18424,16 @@
         <v>108</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -18558,7 +18482,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -18587,10 +18511,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18616,14 +18540,12 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -18672,7 +18594,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>87</v>
@@ -18701,10 +18623,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18730,14 +18652,12 @@
         <v>129</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -18786,7 +18706,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -18815,10 +18735,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18844,13 +18764,13 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -18900,7 +18820,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -18929,10 +18849,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18958,13 +18878,13 @@
         <v>123</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -19014,7 +18934,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19043,10 +18963,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19069,16 +18989,16 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19128,7 +19048,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -19146,7 +19066,7 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
@@ -19157,10 +19077,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19183,19 +19103,19 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -19244,7 +19164,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19253,7 +19173,7 @@
         <v>87</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>99</v>
@@ -19262,7 +19182,7 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
